--- a/output/cv_jepang.xlsx
+++ b/output/cv_jepang.xlsx
@@ -1572,7 +1572,7 @@
       </c>
       <c r="C2" s="113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D2" s="114" t="n"/>
@@ -1630,7 +1630,7 @@
       <c r="E5" s="125" t="n"/>
       <c r="F5" s="126" t="inlineStr">
         <is>
-          <t>ギナ</t>
+          <t>アカ・セブン</t>
         </is>
       </c>
       <c r="G5" s="124" t="n"/>
@@ -1658,7 +1658,7 @@
       <c r="E6" s="121" t="n"/>
       <c r="F6" s="131" t="inlineStr">
         <is>
-          <t>gina</t>
+          <t>jaka sembung</t>
         </is>
       </c>
       <c r="G6" s="120" t="n"/>

--- a/output/cv_jepang.xlsx
+++ b/output/cv_jepang.xlsx
@@ -1338,6 +1338,31 @@
       </spPr>
     </pic>
     <clientData fLocksWithSheet="0"/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1095375" cy="1381125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
   </oneCellAnchor>
 </wsDr>
 </file>
@@ -1572,7 +1597,7 @@
       </c>
       <c r="C2" s="113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D2" s="114" t="n"/>
@@ -1630,7 +1655,7 @@
       <c r="E5" s="125" t="n"/>
       <c r="F5" s="126" t="inlineStr">
         <is>
-          <t>アカ・セブン</t>
+          <t>エサ・アパサ</t>
         </is>
       </c>
       <c r="G5" s="124" t="n"/>
@@ -1658,7 +1683,7 @@
       <c r="E6" s="121" t="n"/>
       <c r="F6" s="131" t="inlineStr">
         <is>
-          <t>jaka sembung</t>
+          <t>ELSA JAPASAL</t>
         </is>
       </c>
       <c r="G6" s="120" t="n"/>
@@ -1685,7 +1710,7 @@
       <c r="E7" s="121" t="n"/>
       <c r="F7" s="82" t="inlineStr">
         <is>
-          <t xml:space="preserve">, , , ,  </t>
+          <t>1111, 2222, 3333, , 4444 43152</t>
         </is>
       </c>
       <c r="G7" s="120" t="n"/>
@@ -1712,7 +1737,7 @@
       <c r="E8" s="120" t="n"/>
       <c r="F8" s="136" t="inlineStr">
         <is>
-          <t>2000年1月1日</t>
+          <t>2005年3月23日</t>
         </is>
       </c>
       <c r="G8" s="120" t="n"/>
@@ -1725,7 +1750,7 @@
       </c>
       <c r="J8" s="120" t="n"/>
       <c r="K8" s="31" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="L8" s="32" t="inlineStr">
         <is>
@@ -1759,7 +1784,7 @@
       <c r="E9" s="121" t="n"/>
       <c r="F9" s="140" t="inlineStr">
         <is>
-          <t>+62</t>
+          <t>+6283845456767</t>
         </is>
       </c>
       <c r="G9" s="141" t="n"/>
@@ -1783,7 +1808,11 @@
 TB</t>
         </is>
       </c>
-      <c r="N9" s="41" t="inlineStr"/>
+      <c r="N9" s="41" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
       <c r="O9" s="42" t="inlineStr">
         <is>
           <t>cm</t>
@@ -1838,7 +1867,11 @@
 BB</t>
         </is>
       </c>
-      <c r="N10" s="58" t="inlineStr"/>
+      <c r="N10" s="58" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="O10" s="51" t="inlineStr">
         <is>
           <t>kg</t>
@@ -1906,7 +1939,7 @@
       <c r="E12" s="151" t="n"/>
       <c r="F12" s="58" t="inlineStr">
         <is>
-          <t>1991年</t>
+          <t>2020年</t>
         </is>
       </c>
       <c r="G12" s="59" t="inlineStr">
@@ -1921,7 +1954,7 @@
       </c>
       <c r="I12" s="58" t="inlineStr">
         <is>
-          <t>1991年</t>
+          <t>2022年</t>
         </is>
       </c>
       <c r="J12" s="59" t="inlineStr">
@@ -1935,7 +1968,11 @@
 SD</t>
         </is>
       </c>
-      <c r="L12" s="82" t="inlineStr"/>
+      <c r="L12" s="82" t="inlineStr">
+        <is>
+          <t>apapun</t>
+        </is>
+      </c>
       <c r="M12" s="120" t="n"/>
       <c r="N12" s="120" t="n"/>
       <c r="O12" s="120" t="n"/>
@@ -1948,7 +1985,7 @@
       <c r="E13" s="151" t="n"/>
       <c r="F13" s="58" t="inlineStr">
         <is>
-          <t>1991年</t>
+          <t>2011年</t>
         </is>
       </c>
       <c r="G13" s="59" t="inlineStr">
@@ -1963,7 +2000,7 @@
       </c>
       <c r="I13" s="58" t="inlineStr">
         <is>
-          <t>1991年</t>
+          <t>2013年</t>
         </is>
       </c>
       <c r="J13" s="59" t="inlineStr">
@@ -1977,7 +2014,11 @@
 SMP</t>
         </is>
       </c>
-      <c r="L13" s="82" t="inlineStr"/>
+      <c r="L13" s="82" t="inlineStr">
+        <is>
+          <t>apapun</t>
+        </is>
+      </c>
       <c r="M13" s="120" t="n"/>
       <c r="N13" s="120" t="n"/>
       <c r="O13" s="120" t="n"/>
@@ -1990,7 +2031,7 @@
       <c r="E14" s="151" t="n"/>
       <c r="F14" s="58" t="inlineStr">
         <is>
-          <t>1991年</t>
+          <t>2023年</t>
         </is>
       </c>
       <c r="G14" s="59" t="inlineStr">
@@ -2005,7 +2046,7 @@
       </c>
       <c r="I14" s="58" t="inlineStr">
         <is>
-          <t>1991年</t>
+          <t>2026年</t>
         </is>
       </c>
       <c r="J14" s="59" t="inlineStr">
@@ -2015,15 +2056,23 @@
       </c>
       <c r="K14" s="49" t="inlineStr">
         <is>
-          <t>普通高校　SMA</t>
-        </is>
-      </c>
-      <c r="L14" s="82" t="inlineStr"/>
+          <t>職業高校　SMK</t>
+        </is>
+      </c>
+      <c r="L14" s="82" t="inlineStr">
+        <is>
+          <t>apapun</t>
+        </is>
+      </c>
       <c r="M14" s="120" t="n"/>
       <c r="N14" s="120" t="n"/>
       <c r="O14" s="120" t="n"/>
       <c r="P14" s="121" t="n"/>
-      <c r="Q14" s="153" t="inlineStr"/>
+      <c r="Q14" s="153" t="inlineStr">
+        <is>
+          <t>英語学科</t>
+        </is>
+      </c>
       <c r="R14" s="150" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1" s="111">
@@ -2117,7 +2166,7 @@
       <c r="E17" s="151" t="n"/>
       <c r="F17" s="58" t="inlineStr">
         <is>
-          <t>1991年</t>
+          <t>2020年</t>
         </is>
       </c>
       <c r="G17" s="70" t="inlineStr">
@@ -2125,22 +2174,30 @@
           <t>1月</t>
         </is>
       </c>
-      <c r="H17" s="157" t="inlineStr"/>
+      <c r="H17" s="157" t="inlineStr">
+        <is>
+          <t>mci</t>
+        </is>
+      </c>
       <c r="I17" s="148" t="n"/>
       <c r="J17" s="148" t="n"/>
       <c r="K17" s="139" t="n"/>
       <c r="L17" s="82" t="inlineStr">
         <is>
-          <t>なし</t>
+          <t>30000円</t>
         </is>
       </c>
       <c r="M17" s="139" t="n"/>
-      <c r="N17" s="49" t="inlineStr"/>
+      <c r="N17" s="49" t="inlineStr">
+        <is>
+          <t>裁縫師</t>
+        </is>
+      </c>
       <c r="O17" s="148" t="n"/>
       <c r="P17" s="139" t="n"/>
       <c r="Q17" s="53" t="inlineStr">
         <is>
-          <t>契約社員 Karyawan kontrak</t>
+          <t>正社員 Karyawan tetap</t>
         </is>
       </c>
       <c r="R17" s="158" t="n"/>
@@ -2340,11 +2397,11 @@
       <c r="G25" s="120" t="n"/>
       <c r="H25" s="121" t="n"/>
       <c r="I25" s="80" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J25" s="81" t="inlineStr">
         <is>
-          <t>ヶ月</t>
+          <t>週間</t>
         </is>
       </c>
       <c r="K25" s="48" t="inlineStr">
@@ -2361,7 +2418,7 @@
       </c>
       <c r="N25" s="153" t="inlineStr">
         <is>
-          <t>1991年 1月 ～ 1991年 1月</t>
+          <t>2025年 1月 ～ 2026年 1月</t>
         </is>
       </c>
       <c r="O25" s="120" t="n"/>
@@ -2376,7 +2433,7 @@
       <c r="E26" s="142" t="n"/>
       <c r="F26" s="162" t="inlineStr">
         <is>
-          <t>英語</t>
+          <t>フランス語</t>
         </is>
       </c>
       <c r="G26" s="120" t="n"/>
@@ -2405,7 +2462,7 @@
       </c>
       <c r="N26" s="153" t="inlineStr">
         <is>
-          <t>( 国)</t>
+          <t>(jerman 国)</t>
         </is>
       </c>
       <c r="O26" s="120" t="n"/>
@@ -2482,18 +2539,30 @@
         </is>
       </c>
       <c r="C29" s="121" t="n"/>
-      <c r="D29" s="82" t="inlineStr"/>
+      <c r="D29" s="82" t="inlineStr">
+        <is>
+          <t>DAVID</t>
+        </is>
+      </c>
       <c r="E29" s="120" t="n"/>
       <c r="F29" s="120" t="n"/>
       <c r="G29" s="120" t="n"/>
       <c r="H29" s="121" t="n"/>
-      <c r="I29" s="89" t="inlineStr"/>
+      <c r="I29" s="89" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="J29" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve"> 歳</t>
         </is>
       </c>
-      <c r="K29" s="153" t="inlineStr"/>
+      <c r="K29" s="153" t="inlineStr">
+        <is>
+          <t>トレーダー</t>
+        </is>
+      </c>
       <c r="L29" s="120" t="n"/>
       <c r="M29" s="120" t="n"/>
       <c r="N29" s="120" t="n"/>
@@ -2666,13 +2735,17 @@
           <t>Nama</t>
         </is>
       </c>
-      <c r="G36" s="166" t="inlineStr"/>
+      <c r="G36" s="166" t="inlineStr">
+        <is>
+          <t>agung</t>
+        </is>
+      </c>
       <c r="H36" s="148" t="n"/>
       <c r="I36" s="148" t="n"/>
       <c r="J36" s="139" t="n"/>
       <c r="K36" s="167" t="inlineStr">
         <is>
-          <t>ちち</t>
+          <t>おとうと</t>
         </is>
       </c>
       <c r="L36" s="139" t="n"/>
@@ -2683,7 +2756,7 @@
       </c>
       <c r="N36" s="169" t="inlineStr">
         <is>
-          <t>+62</t>
+          <t>+6283856577564</t>
         </is>
       </c>
       <c r="O36" s="148" t="n"/>
@@ -2723,7 +2796,11 @@
       <c r="C38" s="148" t="n"/>
       <c r="D38" s="148" t="n"/>
       <c r="E38" s="139" t="n"/>
-      <c r="F38" s="171" t="inlineStr"/>
+      <c r="F38" s="171" t="inlineStr">
+        <is>
+          <t>日本の労働文化について学びたい</t>
+        </is>
+      </c>
       <c r="G38" s="148" t="n"/>
       <c r="H38" s="148" t="n"/>
       <c r="I38" s="148" t="n"/>
@@ -2770,7 +2847,11 @@
       <c r="C40" s="120" t="n"/>
       <c r="D40" s="120" t="n"/>
       <c r="E40" s="121" t="n"/>
-      <c r="F40" s="82" t="inlineStr"/>
+      <c r="F40" s="82" t="inlineStr">
+        <is>
+          <t>フットボール</t>
+        </is>
+      </c>
       <c r="G40" s="120" t="n"/>
       <c r="H40" s="120" t="n"/>
       <c r="I40" s="120" t="n"/>
@@ -2782,7 +2863,11 @@
         </is>
       </c>
       <c r="L40" s="121" t="n"/>
-      <c r="M40" s="153" t="inlineStr"/>
+      <c r="M40" s="153" t="inlineStr">
+        <is>
+          <t>コンピュータを使用できます</t>
+        </is>
+      </c>
       <c r="N40" s="120" t="n"/>
       <c r="O40" s="120" t="n"/>
       <c r="P40" s="120" t="n"/>
@@ -2799,7 +2884,11 @@
       <c r="C41" s="120" t="n"/>
       <c r="D41" s="120" t="n"/>
       <c r="E41" s="121" t="n"/>
-      <c r="F41" s="82" t="inlineStr"/>
+      <c r="F41" s="82" t="inlineStr">
+        <is>
+          <t>チームで働くことができる</t>
+        </is>
+      </c>
       <c r="G41" s="120" t="n"/>
       <c r="H41" s="120" t="n"/>
       <c r="I41" s="120" t="n"/>
@@ -2811,7 +2900,11 @@
         </is>
       </c>
       <c r="L41" s="121" t="n"/>
-      <c r="M41" s="153" t="inlineStr"/>
+      <c r="M41" s="153" t="inlineStr">
+        <is>
+          <t>何もない</t>
+        </is>
+      </c>
       <c r="N41" s="120" t="n"/>
       <c r="O41" s="120" t="n"/>
       <c r="P41" s="120" t="n"/>
@@ -2825,7 +2918,11 @@
         </is>
       </c>
       <c r="J42" s="151" t="n"/>
-      <c r="K42" s="174" t="inlineStr"/>
+      <c r="K42" s="174" t="inlineStr">
+        <is>
+          <t>私はNPDです</t>
+        </is>
+      </c>
       <c r="R42" s="133" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1" s="111">
